--- a/docs/downloads/05/tbl_cooking_alaotra_avaradrano.xlsx
+++ b/docs/downloads/05/tbl_cooking_alaotra_avaradrano.xlsx
@@ -387,12 +387,6 @@
           <t>Autre</t>
         </is>
       </c>
-      <c r="C2">
-        <v>1</v>
-      </c>
-      <c r="D2">
-        <v>0.8</v>
-      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -441,12 +435,6 @@
           <t>Autre</t>
         </is>
       </c>
-      <c r="C5">
-        <v>2</v>
-      </c>
-      <c r="D5">
-        <v>0.3</v>
-      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -476,12 +464,6 @@
         <is>
           <t>Gaz</t>
         </is>
-      </c>
-      <c r="C7">
-        <v>1</v>
-      </c>
-      <c r="D7">
-        <v>0.2</v>
       </c>
     </row>
     <row r="8">

--- a/docs/downloads/05/tbl_cooking_alaotra_avaradrano.xlsx
+++ b/docs/downloads/05/tbl_cooking_alaotra_avaradrano.xlsx
@@ -403,7 +403,7 @@
         <v>49</v>
       </c>
       <c r="D3">
-        <v>40.5</v>
+        <v>54.4</v>
       </c>
     </row>
     <row r="4">
@@ -414,14 +414,14 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Morceaux De Bois Résinés</t>
+          <t>Bois de chauffe</t>
         </is>
       </c>
       <c r="C4">
         <v>71</v>
       </c>
       <c r="D4">
-        <v>58.7</v>
+        <v>78.90000000000001</v>
       </c>
     </row>
     <row r="5">
@@ -451,7 +451,7 @@
         <v>218</v>
       </c>
       <c r="D6">
-        <v>34</v>
+        <v>43</v>
       </c>
     </row>
     <row r="7">
@@ -474,14 +474,14 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Morceaux De Bois Résinés</t>
+          <t>Bois de chauffe</t>
         </is>
       </c>
       <c r="C8">
         <v>420</v>
       </c>
       <c r="D8">
-        <v>65.5</v>
+        <v>82.8</v>
       </c>
     </row>
   </sheetData>
